--- a/ui_runner/templates/graded_analysis_tabs_2026-06-16.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-16.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="3">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G4" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="5">
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="8">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E9" t="n">
         <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>55.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="10">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>937</v>
+        <v>1066</v>
       </c>
       <c r="E11" t="n">
-        <v>560</v>
+        <v>648</v>
       </c>
       <c r="F11" t="n">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="G11" t="n">
-        <v>59.8</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="12">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E13" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>49.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="14">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F14" t="n">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="G14" t="n">
-        <v>23.7</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="15">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="G15" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="16">
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="G16" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="17">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4824</v>
+        <v>5506</v>
       </c>
       <c r="E17" t="n">
-        <v>774</v>
+        <v>946</v>
       </c>
       <c r="F17" t="n">
-        <v>4050</v>
+        <v>4560</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
     </row>
   </sheetData>
@@ -1462,58 +1462,58 @@
         <v>110</v>
       </c>
       <c r="D7" t="n">
-        <v>59.8</v>
+        <v>60.8</v>
       </c>
       <c r="E7" t="n">
-        <v>937</v>
+        <v>1066</v>
       </c>
       <c r="F7" t="n">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="H7" t="n">
-        <v>49.7</v>
+        <v>51.4</v>
       </c>
       <c r="I7" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J7" t="n">
-        <v>23.7</v>
+        <v>25.1</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="L7" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="M7" t="n">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="N7" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="O7" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4824</v>
+        <v>5506</v>
       </c>
       <c r="R7" t="n">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
       <c r="S7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T7" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
       <c r="U7" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>33</v>
       </c>
       <c r="AD7" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="AF7" t="n">
-        <v>55.4</v>
+        <v>50.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
